--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ucaes-my.sharepoint.com/personal/alejandro_lara_uca_es/Documents/Investigación/Cicerone/Hardware/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\cicerone-airlink\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95C5472C-1369-4DAC-928A-E80239CA81D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070614DE-24B8-4AB9-83FF-230473F3A9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{691A75A3-8604-46B0-BF3C-8391BC5A4D41}"/>
+    <workbookView xWindow="8640" yWindow="5535" windowWidth="27450" windowHeight="15345" xr2:uid="{691A75A3-8604-46B0-BF3C-8391BC5A4D41}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="67">
   <si>
     <t>PCB</t>
   </si>
@@ -212,9 +212,6 @@
     <t>3D printing energy consumption</t>
   </si>
   <si>
-    <t>Header for connectin de AC-DC adapter and the switch</t>
-  </si>
-  <si>
     <t>Rocker Switch</t>
   </si>
   <si>
@@ -234,6 +231,12 @@
   </si>
   <si>
     <t>Amazon</t>
+  </si>
+  <si>
+    <t>ABS 3D printed enclosure</t>
+  </si>
+  <si>
+    <t>Header to connect the AC-DC adapter and the switch</t>
   </si>
 </sst>
 </file>
@@ -243,7 +246,7 @@
   <numFmts count="3">
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -300,16 +303,19 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Encabezado 1" xfId="2" builtinId="16"/>
@@ -318,13 +324,13 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="12" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="12" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -347,7 +353,7 @@
   <autoFilter ref="I3:K8" xr:uid="{5AECBEC3-9E2D-40F6-971A-F3F38852F88B}"/>
   <tableColumns count="3">
     <tableColumn id="2" xr3:uid="{50F100A4-1210-4668-A717-95746E047CB3}" name="Quantity" dataDxfId="3"/>
-    <tableColumn id="1" xr3:uid="{F6E42D80-28E9-41C4-BB99-50995C769457}" name="Type" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{F6E42D80-28E9-41C4-BB99-50995C769457}" name="Type" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{A05A8EDB-DBEB-45EE-B247-69B9C0CEA3EA}" name="Device"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -358,7 +364,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{160F51E7-9EEB-46B0-B34D-15F4AC88FDA4}" name="Tabla3" displayName="Tabla3" ref="I11:K13" totalsRowShown="0">
   <autoFilter ref="I11:K13" xr:uid="{160F51E7-9EEB-46B0-B34D-15F4AC88FDA4}"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{1CFB5651-5AF2-4A9D-A351-5D1B73D7487C}" name="Quantity" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{1CFB5651-5AF2-4A9D-A351-5D1B73D7487C}" name="Quantity" dataDxfId="1"/>
     <tableColumn id="1" xr3:uid="{7527D572-A8E6-4052-A3AA-AE48149C6AB2}" name="Type"/>
     <tableColumn id="3" xr3:uid="{B3F1F0BB-820F-4808-BEE2-D8191A265AAF}" name="Device"/>
   </tableColumns>
@@ -375,7 +381,7 @@
     <tableColumn id="4" xr3:uid="{E070E631-582F-41FE-AA40-0936E3E06457}" name="Detailed Description"/>
     <tableColumn id="5" xr3:uid="{E41C2D4A-33D7-4FAB-A982-AFB92F88CD24}" name="Vendor"/>
     <tableColumn id="6" xr3:uid="{B3E552DF-F0CC-4A41-984B-DA55AD1A97CF}" name="Vendor Reference"/>
-    <tableColumn id="7" xr3:uid="{E6008B7E-DEA1-4AAE-8656-7355B427F972}" name="Price" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{E6008B7E-DEA1-4AAE-8656-7355B427F972}" name="Price" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -701,7 +707,7 @@
   <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="86.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -749,14 +755,14 @@
       <c r="E2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="3">
         <v>4.59</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -774,7 +780,7 @@
       <c r="E3" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="3">
         <v>21.3</v>
       </c>
       <c r="I3" t="s">
@@ -803,7 +809,7 @@
       <c r="E4" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <v>6.43</v>
       </c>
       <c r="I4" s="2">
@@ -832,7 +838,7 @@
       <c r="E5" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>30.57</v>
       </c>
       <c r="I5" s="2">
@@ -861,7 +867,7 @@
       <c r="E6" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>25.84</v>
       </c>
       <c r="I6" s="2">
@@ -890,7 +896,7 @@
       <c r="E7" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="3">
         <v>19.36</v>
       </c>
       <c r="I7" s="2">
@@ -908,15 +914,15 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" t="s">
         <v>59</v>
       </c>
-      <c r="C8" t="s">
-        <v>60</v>
-      </c>
       <c r="D8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" s="4">
+        <v>64</v>
+      </c>
+      <c r="F8" s="3">
         <v>0.5</v>
       </c>
       <c r="I8" s="2">
@@ -934,12 +940,12 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" s="4">
+        <v>64</v>
+      </c>
+      <c r="F9" s="3">
         <v>0.65</v>
       </c>
     </row>
@@ -951,22 +957,22 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" s="4">
+        <v>63</v>
+      </c>
+      <c r="F10" s="3">
         <v>0.97</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
     </row>
     <row r="11" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A11">
@@ -984,7 +990,7 @@
       <c r="E11" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="3">
         <v>6</v>
       </c>
       <c r="I11" t="s">
@@ -1010,10 +1016,10 @@
       <c r="D12" t="s">
         <v>27</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="5">
         <v>603048</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="3">
         <v>5.95</v>
       </c>
       <c r="I12" s="2">
@@ -1034,7 +1040,7 @@
         <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
@@ -1042,7 +1048,7 @@
       <c r="E13" t="s">
         <v>25</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="3">
         <v>2.98</v>
       </c>
       <c r="I13" s="2">
@@ -1065,7 +1071,7 @@
       <c r="D14" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="3">
         <v>5</v>
       </c>
     </row>
@@ -1076,13 +1082,16 @@
       <c r="B15" t="s">
         <v>55</v>
       </c>
+      <c r="C15" t="s">
+        <v>65</v>
+      </c>
       <c r="D15" t="s">
         <v>29</v>
       </c>
       <c r="E15" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="3">
         <v>1.77</v>
       </c>
     </row>
@@ -1096,7 +1105,7 @@
       <c r="C16" t="s">
         <v>57</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="3">
         <v>0.8</v>
       </c>
     </row>
@@ -1113,7 +1122,7 @@
       <c r="D17" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1125,7 +1134,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F18" s="1"/>
     </row>
